--- a/data/trans_orig/KC10IN_T-Edad-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Edad-trans_orig.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN autopercibido (escala)</t>
+          <t>KIDSCREEN autopercibido (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57,87</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59,22</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58,67</t>
         </is>
       </c>
     </row>
@@ -571,24 +571,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>56,1; 60,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>57,39; 61,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>57,33; 60,18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>12-15</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57,0</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59,25</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58,23</t>
         </is>
       </c>
     </row>
@@ -621,24 +621,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>54,6; 59,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>56,51; 64,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>56,23; 61,31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8-11</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>57,87</t>
+          <t>57,28</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>59,22</t>
+          <t>59,24</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58,67</t>
+          <t>58,38</t>
         </is>
       </c>
     </row>
@@ -671,135 +671,33 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,03; 60,09</t>
+          <t>55,03; 58,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57,24; 61,36</t>
+          <t>57,44; 62,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,21; 60,2</t>
+          <t>57,0; 60,47</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>57,0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>59,25</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>58,23</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>54,4; 58,88</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>56,27; 64,28</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>56,36; 61,4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>57,28</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>59,24</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>58,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>55,24; 58,75</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>57,44; 63,15</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>56,9; 60,29</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="4">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A4:A5"/>
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/KC10IN_T-Edad-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Edad-trans_orig.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>56,1; 60,14</t>
+          <t>55,97; 59,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,39; 61,43</t>
+          <t>57,27; 61,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57,33; 60,18</t>
+          <t>57,32; 60,28</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,6; 59,25</t>
+          <t>54,43; 59,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56,51; 64,12</t>
+          <t>56,42; 64,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,23; 61,31</t>
+          <t>56,3; 61,7</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55,03; 58,74</t>
+          <t>55,01; 58,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57,44; 62,69</t>
+          <t>57,3; 62,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,0; 60,47</t>
+          <t>57,09; 60,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KC10IN_T-Edad-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Edad-trans_orig.xlsx
@@ -495,12 +495,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>57,87</t>
+          <t>59,13</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>59,22</t>
+          <t>57,79</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58,67</t>
+          <t>58,56</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55,97; 59,76</t>
+          <t>57,17; 61,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,27; 61,35</t>
+          <t>55,97; 59,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57,32; 60,28</t>
+          <t>57,12; 60,03</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>57,0</t>
+          <t>58,81</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>59,25</t>
+          <t>58,02</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58,23</t>
+          <t>58,47</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,43; 59,02</t>
+          <t>56,22; 63,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56,42; 64,07</t>
+          <t>56,5; 59,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,3; 61,7</t>
+          <t>56,96; 61,25</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>57,28</t>
+          <t>58,93</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>59,24</t>
+          <t>57,94</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58,38</t>
+          <t>58,51</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55,01; 58,64</t>
+          <t>57,29; 62,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57,3; 62,15</t>
+          <t>56,75; 59,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,09; 60,49</t>
+          <t>57,36; 60,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KC10IN_T-Edad-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -97,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -110,6 +112,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -489,7 +494,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN autopercibido (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN autopercibido (escala) (tasa de respuesta: 29,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -546,147 +551,162 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>59,13</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>57,79</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>58,56</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>59.12803945908814</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>57.78963334542336</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>58.56346413447014</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>57,17; 61,29</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>55,97; 59,97</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>57,12; 60,03</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>57.16869543532562</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>55.97165893632175</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>57.115376071714</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>61.29343386231113</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>59.96640204205324</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>60.03097783666588</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>12-15</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>58,81</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>58,02</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>58,47</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>56,22; 63,1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>56,5; 59,73</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>56,96; 61,25</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>58.81034844017066</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>58.01805447781175</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>58.47432912257418</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>58,93</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>57,94</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>58,51</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>56.22398649278241</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>56.49839809419214</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>56.96394377511831</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>57,29; 62,02</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>56,75; 59,14</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>57,36; 60,14</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>63.0977691162274</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>59.72911639604299</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>61.25006448387773</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>58.92573356494936</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>57.93558560135788</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>58.50662137489838</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>57.28806576354001</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>56.74706226701043</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>57.3591037734431</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>62.02226257352562</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>59.1375121271623</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>60.13804743013878</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -695,9 +715,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A4:A6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
